--- a/data/externalStats/File1/RPT_RPT3439421614472VV_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT3439421614472VV_externalStats.xlsx
@@ -2060,13 +2060,13 @@
         <v>2948530.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2824301</v>
+        <v>2824325</v>
       </c>
       <c r="G25" s="41" t="n">
         <v>25.52310030986256</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.44774246044112</v>
+        <v>24.44795020948028</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>28321869.63325635</v>
+        <v>13947091.25920994</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>37842.22928475848</v>
+        <v>37842.22928475847</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>12577936.89957107</v>
+        <v>6184152.308955775</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1010.22492</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>11053681.77593989</v>
+        <v>5434726.873170443</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>14824.51869790836</v>
@@ -2291,13 +2291,13 @@
         <v>5319254.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5520183</v>
+        <v>5520207</v>
       </c>
       <c r="G28" s="67" t="n">
         <v>36.1504838183597</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.51602533606992</v>
+        <v>37.51618844381618</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>10006630.44429191</v>
+        <v>4938392.254166341</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>12396.8159518388</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>9804357.984809294</v>
+        <v>4820476.009197904</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>487.1813100000001</v>
@@ -2445,13 +2445,13 @@
         <v>5538692.390034735</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5928219</v>
+        <v>5928243</v>
       </c>
       <c r="G30" s="72" t="n">
         <v>35.5354179928318</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.03456218241544</v>
+        <v>38.0347161628086</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>7349724.884596496</v>
+        <v>3613614.734926611</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>563.805105</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>6188704.374589608</v>
+        <v>3055090.697660313</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>3352.283312</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5634318.814640129</v>
+        <v>2770206.750531396</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>752.332995</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5231411.651656954</v>
+        <v>2587198.057487481</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>780.9839425823878</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>5120351.540857111</v>
+        <v>2517506.174254747</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>10663.33630118522</v>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2901313.69343935</v>
+        <v>1426479.232607681</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>354.0840958925123</v>
+        <v>354.0840958925122</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2870215.222719257</v>
+        <v>1411189.151170301</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2997.03719227378</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2681546.565749676</v>
+        <v>1318427.06149359</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>5572.101234209256</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2091980.223739786</v>
+        <v>1035609.308444081</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>5564.442124999997</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1948582.403595467</v>
+        <v>958053.0151011046</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>379.6218</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1941215.895906649</v>
+        <v>954431.1488207688</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>2057.340789</v>
@@ -3248,13 +3248,13 @@
         <v>50296108.41710961</v>
       </c>
       <c r="F41" s="40" t="n">
-        <v>28661163</v>
+        <v>28661187</v>
       </c>
       <c r="G41" s="41" t="n">
         <v>42.46418414934163</v>
       </c>
       <c r="H41" s="42" t="n">
-        <v>24.19815253842335</v>
+        <v>24.19817280123198</v>
       </c>
       <c r="I41" s="31" t="n"/>
       <c r="J41" s="31" t="n"/>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1886765.755512452</v>
+        <v>927659.8297936219</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>432.34705</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1789465.390993749</v>
+        <v>882889.424784031</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>2313.128836677755</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1768589.080728072</v>
+        <v>868200.3466968584</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>84625120.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57905081</v>
+        <v>57905105</v>
       </c>
       <c r="G44" s="67" t="n">
         <v>55.73554683789877</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13727357569123</v>
+        <v>38.13728938250041</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1501367.534266635</v>
+        <v>745681.8596899565</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>3118.807607</v>
@@ -3598,13 +3598,13 @@
         <v>84894979.79706067</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58345311</v>
+        <v>58345335</v>
       </c>
       <c r="G46" s="72" t="n">
         <v>55.56026898065463</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18460385607141</v>
+        <v>38.18461956308329</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>49532560.644583</v>
+        <v>24368596.31234279</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>6670.893598846876</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>42381311.56098316</v>
+        <v>20862719.14788772</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>56332.87391490716</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>10959706.68278566</v>
+        <v>5408579.53006674</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>13939.77200165373</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>8567448.901922544</v>
+        <v>4215924.230025964</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>10800.2529744</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>8284801.961749366</v>
+        <v>4073360.964526771</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>21984.01577959447</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>7802523.646432152</v>
+        <v>3843524.365282453</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>4030.61368395</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3366314.565705817</v>
+        <v>1672063.656524569</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>9565.774205806498</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2578527.707882969</v>
+        <v>1261629.68190707</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>247.9364052213409</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>GROWTH HORMONES</t>
+          <t>ORAL ANTICOAGULANTS</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2540465.730080406</v>
+        <v>1254097.55475457</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>390.6887153</v>
+        <v>6706.464778411765</v>
       </c>
     </row>
     <row r="58">
@@ -4310,37 +4310,37 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410514</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.73362042244</v>
+        <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831596</v>
+        <v>276.6926051831595</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842926</v>
+        <v>5127.579913842927</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -4352,21 +4352,21 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>ORAL ANTICOAGULANTS</t>
+          <t>GROWTH HORMONES</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2533502.646275916</v>
+        <v>1241148.093831338</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>6706.464778411765</v>
+        <v>390.6887153000001</v>
       </c>
     </row>
     <row r="59">
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -4412,13 +4412,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.577740853268</v>
+        <v>405.5777408532679</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597413</v>
+        <v>4497.071348597412</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.649089450681</v>
+        <v>4902.64908945068</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>460.4035115416655</v>
+        <v>460.4035115416654</v>
       </c>
       <c r="Y59" s="131" t="n">
         <v>4931.9450340127</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1652160.935343546</v>
+        <v>813148.0153978789</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>4793.408093083508</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1510990.688298312</v>
+        <v>729076.8075873244</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>0</v>
@@ -4544,16 +4544,16 @@
         <v>6511</v>
       </c>
       <c r="F61" s="131" t="n">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="G61" s="131" t="n">
         <v>2450</v>
       </c>
       <c r="H61" s="132" t="n">
-        <v>33507</v>
+        <v>33517</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2710.474833260433</v>
+        <v>2710.474833260434</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>710.0358767901117</v>
@@ -4562,13 +4562,13 @@
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894161</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2848.462218149934</v>
+        <v>2848.462218149935</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>760.0653829141091</v>
@@ -4577,22 +4577,22 @@
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193558</v>
+        <v>560.6592858193557</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657396</v>
+        <v>4406.934138657397</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888539</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252181</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4652.873020834729</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1349853.757651036</v>
+        <v>667329.0243751658</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>4568.302288</v>
+        <v>4568.302287999999</v>
       </c>
     </row>
     <row r="62">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1322832.935920637</v>
+        <v>638287.7282841182</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>259.41946992</v>
@@ -4715,22 +4715,22 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.11633837899</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>410.0571917407942</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810829</v>
+        <v>4860.049068810828</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375967</v>
+        <v>7725.953271892038</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303852</v>
+        <v>2462.699113100389</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224321</v>
@@ -4742,22 +4742,22 @@
         <v>5497.210231316723</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.61799146968</v>
+        <v>8533.720644266217</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.764857629416</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>448.2773868014747</v>
+        <v>448.2773868014774</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>165.507746920809</v>
+        <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292747</v>
+        <v>9544.356383217537</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>1299453.678818036</v>
+        <v>627006.8684719881</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>1149418.680106638</v>
+        <v>569915.2153228831</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>2709.978884373738</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>1054904.343022584</v>
+        <v>525158.3216981211</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>182.0238604167168</v>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>989013.9075189302</v>
+        <v>489465.8634541501</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2740.1603206045</v>
@@ -5060,34 +5060,34 @@
         <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996084</v>
+        <v>32493.07951996085</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233702</v>
+        <v>1367.292909233701</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>3448.841300635404</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288215</v>
+        <v>41401.49046288216</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700119</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>1383.30169709932</v>
+        <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>971988.9705695324</v>
+        <v>481055.6571768877</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>4489.793987714651</v>
@@ -5117,16 +5117,16 @@
         <v>7613</v>
       </c>
       <c r="F68" s="143" t="n">
-        <v>2937</v>
+        <v>2947</v>
       </c>
       <c r="G68" s="143" t="n">
         <v>8960</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>45224</v>
+        <v>45234</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.68525504045</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>6296.901716791413</v>
@@ -5138,37 +5138,37 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342014</v>
+        <v>62122.79635693621</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.39453944851</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411189</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870798</v>
+        <v>2439.116021870797</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>14003.7821663689</v>
+        <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630283</v>
+        <v>64372.37424909938</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.82584599084</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275839</v>
+        <v>6878.522835275841</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2535.996836477479</v>
+        <v>2535.996836477478</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.45769810819</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>867424.3467601602</v>
+        <v>429111.3872944924</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>2703.960876253711</v>
@@ -5677,7 +5677,7 @@
         <v>42.9367881661009</v>
       </c>
       <c r="L76" s="131" t="n">
-        <v>12.11019747209272</v>
+        <v>12.11019747209273</v>
       </c>
       <c r="M76" s="131" t="n">
         <v>0</v>
@@ -5686,10 +5686,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399727</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -5698,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05577202167449</v>
+        <v>45.0557720216745</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -5744,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -5759,10 +5759,10 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328252</v>
+        <v>51.04086451328254</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
         <v>428.5976195989508</v>
@@ -5774,13 +5774,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239313</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>486.2580302793616</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217548</v>
+        <v>542.1736389217547</v>
       </c>
     </row>
     <row r="78">
@@ -5872,13 +5872,13 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486969</v>
+        <v>2697.069435486968</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.2101537440751</v>
+        <v>51.21015374407511</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
@@ -5887,34 +5887,34 @@
         <v>2871.031146169767</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277549</v>
+        <v>2967.818385277547</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936018</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.05193641638</v>
+        <v>3183.051936416378</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>3245.047703850661</v>
+        <v>3245.047703850659</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598369</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3500.166070420847</v>
+        <v>3500.166070420846</v>
       </c>
     </row>
     <row r="80">
@@ -6299,7 +6299,7 @@
         <v>252563.5334183737</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897596</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>1395.789484341961</v>
@@ -6314,7 +6314,7 @@
         <v>253578.7535428639</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879695</v>
+        <v>58272.40781879696</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
@@ -6366,7 +6366,7 @@
         <v>252748.9987789858</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323378</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
         <v>3262.529604664169</v>
@@ -6381,7 +6381,7 @@
         <v>253794.7078852251</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624421</v>
+        <v>58414.03815624422</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>3611.957540811319</v>
@@ -6876,13 +6876,13 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748546</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471617</v>
+        <v>287.3141106471616</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -6891,13 +6891,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901525</v>
+        <v>3803.886503901526</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483363</v>
+        <v>289.1404209483361</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -6964,13 +6964,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665506</v>
+        <v>456.6186053665505</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049632</v>
+        <v>5331.246709049631</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -6979,13 +6979,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>516.3191201840586</v>
+        <v>516.3191201840584</v>
       </c>
       <c r="Y95" s="131" t="n">
         <v>5418.203064292061</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5934.52218447612</v>
+        <v>5934.522184476119</v>
       </c>
     </row>
     <row r="96">
@@ -7068,16 +7068,16 @@
         <v>6698</v>
       </c>
       <c r="F97" s="131" t="n">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="G97" s="131" t="n">
         <v>3193</v>
       </c>
       <c r="H97" s="132" t="n">
-        <v>35946</v>
+        <v>35956</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5407.544268747402</v>
+        <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>821.8541182771896</v>
@@ -7086,37 +7086,37 @@
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410619</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>7069.112073998889</v>
+        <v>7069.112073998888</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427484</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.3963514921278</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.6295457533571</v>
+        <v>300.629545753357</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008077</v>
+        <v>571.6795744008076</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073776</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299142</v>
       </c>
       <c r="Z97" s="132" t="n">
         <v>8153.039091255576</v>
@@ -7211,7 +7211,7 @@
         <v>3922</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2315.017224862706</v>
+        <v>2315.11633837875</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>410.0571917407797</v>
@@ -7220,13 +7220,13 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571753</v>
+        <v>6263.925439571751</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136659</v>
+        <v>9129.829642652701</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2462.596460303757</v>
+        <v>2462.699113100301</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>422.0057850224257</v>
@@ -7235,13 +7235,13 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971808</v>
+        <v>6975.373307971809</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.88372092121</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2639.658250704873</v>
+        <v>2639.764857629547</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>448.277386801492</v>
@@ -7250,10 +7250,10 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578744</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11118.07690593058</v>
       </c>
     </row>
     <row r="100">
@@ -7504,10 +7504,10 @@
         <v>256655.8101514259</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820966</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977366</v>
+        <v>4844.630784977365</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469095.27040621</v>
@@ -7519,7 +7519,7 @@
         <v>257981.429150564</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589627</v>
+        <v>59655.70951589628</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -7541,16 +7541,16 @@
         <v>7839</v>
       </c>
       <c r="F104" s="143" t="n">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G104" s="143" t="n">
         <v>10545</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>48702</v>
+        <v>48712</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204109</v>
+        <v>1147367.743317625</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>257480.6278357822</v>
@@ -7562,10 +7562,10 @@
         <v>15819.80035996352</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1480444.654269834</v>
+        <v>1480444.75338335</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.46897923</v>
+        <v>1160502.571632026</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>259202.0803003969</v>
@@ -7577,22 +7577,22 @@
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195764</v>
+        <v>1497344.281848561</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554632</v>
+        <v>1172449.123161557</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>260673.2307205009</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272169</v>
+        <v>60950.0349927217</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.35198903</v>
+        <v>1513285.458595955</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -8584,13 +8584,13 @@
         <v>2948530.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2824301</v>
+        <v>2824325</v>
       </c>
       <c r="G25" s="41" t="n">
         <v>25.52310030986256</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.44774246044112</v>
+        <v>24.44795020948028</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>36479108.3909279</v>
+        <v>17752281.70560132</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>47681.20374516814</v>
+        <v>47681.20374516815</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>16000083.88751766</v>
+        <v>7768848.071072222</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1224.14004681</v>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>11253453.56619038</v>
+        <v>5514102.032492951</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>13973.95203328434</v>
@@ -8815,13 +8815,13 @@
         <v>5319254.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5520183</v>
+        <v>5520207</v>
       </c>
       <c r="G28" s="67" t="n">
         <v>36.1504838183597</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.51602533606992</v>
+        <v>37.51618844381618</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>11038405.43053451</v>
+        <v>5359702.82028476</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>14231.53794999202</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>10130759.10811187</v>
+        <v>4918994.732080923</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>496.3110877493999</v>
@@ -8969,13 +8969,13 @@
         <v>5538692.390034735</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5928219</v>
+        <v>5928243</v>
       </c>
       <c r="G30" s="72" t="n">
         <v>35.5354179928318</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.03456218241544</v>
+        <v>38.0347161628086</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>9576725.592281302</v>
+        <v>4649983.504325577</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>683.19083598375</v>
+        <v>683.1908359837498</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>8104574.014232036</v>
+        <v>3957740.45165328</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>4224.61447544864</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>7261041.493413353</v>
+        <v>3525602.027879831</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>911.6395066912501</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5596493.161870112</v>
+        <v>2740020.605216204</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>795.784626769313</v>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>5451507.926517456</v>
+        <v>2646982.174412259</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>10927.57377472858</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3240440.171817308</v>
+        <v>1573397.211866339</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3238.95803443412</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3129242.204697554</v>
+        <v>1519404.987923101</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>360.8044705626895</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2787119.15608395</v>
+        <v>1353286.984731588</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>5710.17790279296</v>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2230525.508568964</v>
+        <v>1083032.683862499</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2223.40933748808</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2065048.249427686</v>
+        <v>1002685.124779452</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>386.7359125319999</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>2033725.047396484</v>
+        <v>988547.3361576474</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>0</v>
@@ -9772,13 +9772,13 @@
         <v>50296108.41710961</v>
       </c>
       <c r="F41" s="40" t="n">
-        <v>28661163</v>
+        <v>28661187</v>
       </c>
       <c r="G41" s="41" t="n">
         <v>42.46418414934163</v>
       </c>
       <c r="H41" s="42" t="n">
-        <v>24.19815253842335</v>
+        <v>24.19817280123198</v>
       </c>
       <c r="I41" s="31" t="n"/>
       <c r="J41" s="31" t="n"/>
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1751703.99415768</v>
+        <v>854741.5148206135</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>2220.603683210645</v>
+        <v>2220.603683210644</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1736170.479638997</v>
+        <v>852809.6305175911</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>5750.8412192</v>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1625494.155551699</v>
+        <v>789259.4328676487</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1968.716811057299</v>
@@ -10003,13 +10003,13 @@
         <v>84625120.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57905081</v>
+        <v>57905105</v>
       </c>
       <c r="G44" s="67" t="n">
         <v>55.73554683789877</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13727357569123</v>
+        <v>38.13728938250041</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1591026.841272945</v>
+        <v>787251.353069991</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>3262.52226153056</v>
@@ -10122,13 +10122,13 @@
         <v>84894979.79706067</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58345311</v>
+        <v>58345335</v>
       </c>
       <c r="G46" s="72" t="n">
         <v>55.56026898065463</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18460385607141</v>
+        <v>38.18461956308329</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>56378668.00369059</v>
+        <v>27397328.89423775</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>7083.015834286237</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>50483914.26914035</v>
+        <v>24556522.46091366</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>65432.22259011088</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>12364013.2819005</v>
+        <v>6057976.219727449</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>15396.93946398233</v>
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>9858834.583375711</v>
+        <v>4801978.350553673</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>4920.984644414999</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>9752260.173932118</v>
+        <v>4740973.427386988</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>11672.04939449357</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>8742251.564037921</v>
+        <v>4244804.257125752</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>22528.77969061282</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3543836.866727677</v>
+        <v>1753731.953259998</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>10006.56508121006</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2972569.391933222</v>
+        <v>1438366.850709246</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>250.2622030851889</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2722266.676301664</v>
+        <v>1310090.837970176</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>397.6703226424111</v>
@@ -10834,37 +10834,37 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410514</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.73362042244</v>
+        <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831596</v>
+        <v>276.6926051831595</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842926</v>
+        <v>5127.579913842927</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1884836.830838859</v>
+        <v>926003.2202334554</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>6395.6232032</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -10936,13 +10936,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.577740853268</v>
+        <v>405.5777408532679</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597413</v>
+        <v>4497.071348597412</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.649089450681</v>
+        <v>4902.64908945068</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -10951,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>460.4035115416655</v>
+        <v>460.4035115416654</v>
       </c>
       <c r="Y59" s="131" t="n">
         <v>4931.9450340127</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1853000.075609566</v>
+        <v>880214.7487322812</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1650870.480105933</v>
+        <v>802764.3704953031</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>4575.883233819379</v>
@@ -11068,16 +11068,16 @@
         <v>6511</v>
       </c>
       <c r="F61" s="131" t="n">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="G61" s="131" t="n">
         <v>2450</v>
       </c>
       <c r="H61" s="132" t="n">
-        <v>33507</v>
+        <v>33517</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2710.474833260433</v>
+        <v>2710.474833260434</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>710.0358767901117</v>
@@ -11086,13 +11086,13 @@
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894161</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2848.462218149934</v>
+        <v>2848.462218149935</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>760.0653829141091</v>
@@ -11101,22 +11101,22 @@
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193558</v>
+        <v>560.6592858193557</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657396</v>
+        <v>4406.934138657397</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888539</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252181</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4652.873020834729</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1605700.344382237</v>
+        <v>762742.0763621966</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1345752.634099762</v>
+        <v>639261.3428740714</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>243.9373159551744</v>
@@ -11239,22 +11239,22 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.11633837899</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>410.0571917407942</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810829</v>
+        <v>4860.049068810828</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375967</v>
+        <v>7725.953271892038</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303852</v>
+        <v>2462.699113100389</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224321</v>
@@ -11266,22 +11266,22 @@
         <v>5497.210231316723</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.61799146968</v>
+        <v>8533.720644266217</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.764857629416</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>448.2773868014747</v>
+        <v>448.2773868014774</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>165.507746920809</v>
+        <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292747</v>
+        <v>9544.356383217537</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>1199423.94289529</v>
+        <v>591936.7819315405</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2847.030358073276</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>1106322.558871141</v>
+        <v>541930.0195048057</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>2939.919686845487</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>1079212.503711125</v>
+        <v>535243.0648755158</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>175.8428860210854</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>989452.3065636669</v>
+        <v>486934.0599475541</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>4601.05108273022</v>
@@ -11584,34 +11584,34 @@
         <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996084</v>
+        <v>32493.07951996085</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233702</v>
+        <v>1367.292909233701</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>3448.841300635404</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288215</v>
+        <v>41401.49046288216</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700119</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>1383.30169709932</v>
+        <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>828700.2214457954</v>
+        <v>406621.463842111</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>2581.255131689318</v>
@@ -11641,16 +11641,16 @@
         <v>7613</v>
       </c>
       <c r="F68" s="143" t="n">
-        <v>2937</v>
+        <v>2947</v>
       </c>
       <c r="G68" s="143" t="n">
         <v>8960</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>45224</v>
+        <v>45234</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.68525504045</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>6296.901716791413</v>
@@ -11662,37 +11662,37 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342014</v>
+        <v>62122.79635693621</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.39453944851</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411189</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870798</v>
+        <v>2439.116021870797</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>14003.7821663689</v>
+        <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630283</v>
+        <v>64372.37424909938</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.82584599084</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275839</v>
+        <v>6878.522835275841</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2535.996836477479</v>
+        <v>2535.996836477478</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.45769810819</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>716526.359074851</v>
+        <v>355502.8640799564</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>509.1231169767389</v>
@@ -12201,7 +12201,7 @@
         <v>42.9367881661009</v>
       </c>
       <c r="L76" s="131" t="n">
-        <v>12.11019747209272</v>
+        <v>12.11019747209273</v>
       </c>
       <c r="M76" s="131" t="n">
         <v>0</v>
@@ -12210,10 +12210,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399727</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -12222,13 +12222,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05577202167449</v>
+        <v>45.0557720216745</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -12268,7 +12268,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -12283,10 +12283,10 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328252</v>
+        <v>51.04086451328254</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
         <v>428.5976195989508</v>
@@ -12298,13 +12298,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239313</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>486.2580302793616</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217548</v>
+        <v>542.1736389217547</v>
       </c>
     </row>
     <row r="78">
@@ -12396,13 +12396,13 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486969</v>
+        <v>2697.069435486968</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.2101537440751</v>
+        <v>51.21015374407511</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
@@ -12411,34 +12411,34 @@
         <v>2871.031146169767</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277549</v>
+        <v>2967.818385277547</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936018</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.05193641638</v>
+        <v>3183.051936416378</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>3245.047703850661</v>
+        <v>3245.047703850659</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598369</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3500.166070420847</v>
+        <v>3500.166070420846</v>
       </c>
     </row>
     <row r="80">
@@ -12823,7 +12823,7 @@
         <v>252563.5334183737</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897596</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>1395.789484341961</v>
@@ -12838,7 +12838,7 @@
         <v>253578.7535428639</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879695</v>
+        <v>58272.40781879696</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
@@ -12890,7 +12890,7 @@
         <v>252748.9987789858</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323378</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
         <v>3262.529604664169</v>
@@ -12905,7 +12905,7 @@
         <v>253794.7078852251</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624421</v>
+        <v>58414.03815624422</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>3611.957540811319</v>
@@ -13400,13 +13400,13 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748546</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471617</v>
+        <v>287.3141106471616</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -13415,13 +13415,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901525</v>
+        <v>3803.886503901526</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483363</v>
+        <v>289.1404209483361</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -13430,13 +13430,13 @@
         <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -13488,13 +13488,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665506</v>
+        <v>456.6186053665505</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049632</v>
+        <v>5331.246709049631</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -13503,13 +13503,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>516.3191201840586</v>
+        <v>516.3191201840584</v>
       </c>
       <c r="Y95" s="131" t="n">
         <v>5418.203064292061</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5934.52218447612</v>
+        <v>5934.522184476119</v>
       </c>
     </row>
     <row r="96">
@@ -13592,16 +13592,16 @@
         <v>6698</v>
       </c>
       <c r="F97" s="131" t="n">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="G97" s="131" t="n">
         <v>3193</v>
       </c>
       <c r="H97" s="132" t="n">
-        <v>35946</v>
+        <v>35956</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5407.544268747402</v>
+        <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>821.8541182771896</v>
@@ -13610,37 +13610,37 @@
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410619</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>7069.112073998889</v>
+        <v>7069.112073998888</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427484</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.3963514921278</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.6295457533571</v>
+        <v>300.629545753357</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008077</v>
+        <v>571.6795744008076</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073776</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299142</v>
       </c>
       <c r="Z97" s="132" t="n">
         <v>8153.039091255576</v>
@@ -13735,7 +13735,7 @@
         <v>3922</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2315.017224862706</v>
+        <v>2315.11633837875</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>410.0571917407797</v>
@@ -13744,13 +13744,13 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571753</v>
+        <v>6263.925439571751</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136659</v>
+        <v>9129.829642652701</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2462.596460303757</v>
+        <v>2462.699113100301</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>422.0057850224257</v>
@@ -13759,13 +13759,13 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971808</v>
+        <v>6975.373307971809</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.88372092121</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2639.658250704873</v>
+        <v>2639.764857629547</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>448.277386801492</v>
@@ -13774,10 +13774,10 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578744</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11118.07690593058</v>
       </c>
     </row>
     <row r="100">
@@ -14028,10 +14028,10 @@
         <v>256655.8101514259</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820966</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977366</v>
+        <v>4844.630784977365</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469095.27040621</v>
@@ -14043,7 +14043,7 @@
         <v>257981.429150564</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589627</v>
+        <v>59655.70951589628</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -14065,16 +14065,16 @@
         <v>7839</v>
       </c>
       <c r="F104" s="143" t="n">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G104" s="143" t="n">
         <v>10545</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>48702</v>
+        <v>48712</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204109</v>
+        <v>1147367.743317625</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>257480.6278357822</v>
@@ -14086,10 +14086,10 @@
         <v>15819.80035996352</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1480444.654269834</v>
+        <v>1480444.75338335</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.46897923</v>
+        <v>1160502.571632026</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>259202.0803003969</v>
@@ -14101,22 +14101,22 @@
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195764</v>
+        <v>1497344.281848561</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554632</v>
+        <v>1172449.123161557</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>260673.2307205009</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272169</v>
+        <v>60950.0349927217</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.35198903</v>
+        <v>1513285.458595955</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -15108,13 +15108,13 @@
         <v>2948530.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2824301</v>
+        <v>2824325</v>
       </c>
       <c r="G25" s="41" t="n">
         <v>25.52310030986256</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.44774246044112</v>
+        <v>24.44795020948028</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45226804.3126963</v>
+        <v>21799952.45671339</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>57217.44053621583</v>
@@ -15226,7 +15226,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>20607001.6923678</v>
+        <v>9845442.547980569</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1458.856659385349</v>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>12848232.3139037</v>
+        <v>6251700.340033773</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>15724.71578175682</v>
@@ -15339,13 +15339,13 @@
         <v>5319254.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5520183</v>
+        <v>5520207</v>
       </c>
       <c r="G28" s="67" t="n">
         <v>36.1504838183597</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.51602533606992</v>
+        <v>37.51618844381618</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -15380,10 +15380,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>12634053.25706936</v>
+        <v>6036193.297187558</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>814.1858468752743</v>
+        <v>814.1858468752741</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>11115569.71666375</v>
+        <v>5346405.256682637</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>13662.27643199234</v>
@@ -15493,13 +15493,13 @@
         <v>5538692.390034735</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5928219</v>
+        <v>5928243</v>
       </c>
       <c r="G30" s="72" t="n">
         <v>35.5354179928318</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.03456218241544</v>
+        <v>38.0347161628086</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>10859073.60707207</v>
+        <v>5188158.22499385</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>509.4881471291466</v>
@@ -15597,10 +15597,10 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>10652124.34036913</v>
+        <v>5116109.913329908</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>5158.465505246561</v>
+        <v>5158.46550524656</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>9474059.733016083</v>
+        <v>4526437.770522078</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>1086.43726570423</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6266593.152010616</v>
+        <v>3016928.039253375</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>817.0916674748538</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>5844619.07684657</v>
+        <v>2811165.145131119</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>11198.35905286636</v>
@@ -15899,10 +15899,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3679671.173030181</v>
+        <v>1769860.997125465</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>3491.467202798605</v>
+        <v>3491.467202798604</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3501203.478154545</v>
+        <v>1672775.991750769</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>370.475820109104</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2921135.693464905</v>
+        <v>1405017.972548108</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>5851.676111224171</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2569349.041505356</v>
+        <v>1235814.409149306</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2396.746329438651</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2460069.301430025</v>
+        <v>1200938.715336686</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>8051.177706879998</v>
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>2393085.741691884</v>
+        <v>1152224.363178569</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>0</v>
@@ -16296,13 +16296,13 @@
         <v>50296108.41710961</v>
       </c>
       <c r="F41" s="40" t="n">
-        <v>28661163</v>
+        <v>28661187</v>
       </c>
       <c r="G41" s="41" t="n">
         <v>42.46418414934163</v>
       </c>
       <c r="H41" s="42" t="n">
-        <v>24.19815253842335</v>
+        <v>24.19817280123198</v>
       </c>
       <c r="I41" s="31" t="n"/>
       <c r="J41" s="31" t="n"/>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2270228.596905557</v>
+        <v>1084651.011112135</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>397.0037510097247</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1944109.076606213</v>
+        <v>910247.1425370253</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>0</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1881079.821863847</v>
+        <v>904768.2938622283</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2122.197973647326</v>
@@ -16527,13 +16527,13 @@
         <v>84625120.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57905081</v>
+        <v>57905105</v>
       </c>
       <c r="G44" s="67" t="n">
         <v>55.73554683789877</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13727357569123</v>
+        <v>38.13728938250041</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -16559,19 +16559,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>TRULICITY</t>
+          <t>TRELEGY ELLIPTA</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1737807.438772059</v>
+        <v>845305.2776773213</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>2131.779535882219</v>
+        <v>3412.859287341889</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -16646,13 +16646,13 @@
         <v>84894979.79706067</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58345311</v>
+        <v>58345335</v>
       </c>
       <c r="G46" s="72" t="n">
         <v>55.56026898065463</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18460385607141</v>
+        <v>38.18461956308329</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>68237083.39700042</v>
+        <v>32624675.46828424</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>7644.8948434862</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>59303428.40723624</v>
+        <v>28574508.0289522</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>74258.41862736085</v>
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>14161678.89840377</v>
+        <v>6890345.649355425</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>17288.14627740435</v>
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>12570488.95517502</v>
+        <v>6026337.701080014</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>5845.4184011803</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>11166840.99374089</v>
+        <v>5377358.192480322</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>12582.00236528829</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>9295322.787081428</v>
+        <v>4470896.578239454</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>23087.04285134621</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3792977.495520293</v>
+        <v>1870147.302198512</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>10467.66760015222</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3503361.50212251</v>
+        <v>1677293.405799884</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>251.6363426182479</v>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2992872.210468845</v>
+        <v>1418240.794503649</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>407.8824965278682</v>
@@ -17358,37 +17358,37 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410514</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.73362042244</v>
+        <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831596</v>
+        <v>276.6926051831595</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842926</v>
+        <v>5127.579913842927</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -17400,7 +17400,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2676412.222065229</v>
+        <v>1306863.614257138</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>8953.872484479998</v>
@@ -17445,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -17460,13 +17460,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.577740853268</v>
+        <v>405.5777408532679</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597413</v>
+        <v>4497.071348597412</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.649089450681</v>
+        <v>4902.64908945068</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -17475,7 +17475,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>460.4035115416655</v>
+        <v>460.4035115416654</v>
       </c>
       <c r="Y59" s="131" t="n">
         <v>4931.9450340127</v>
@@ -17492,7 +17492,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>2224356.593429326</v>
+        <v>1041461.23153076</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>2013256.073042416</v>
+        <v>942622.3094854484</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>0</v>
@@ -17592,16 +17592,16 @@
         <v>6511</v>
       </c>
       <c r="F61" s="131" t="n">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="G61" s="131" t="n">
         <v>2450</v>
       </c>
       <c r="H61" s="132" t="n">
-        <v>33507</v>
+        <v>33517</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2710.474833260433</v>
+        <v>2710.474833260434</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>710.0358767901117</v>
@@ -17610,13 +17610,13 @@
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894161</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2848.462218149934</v>
+        <v>2848.462218149935</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>760.0653829141091</v>
@@ -17625,22 +17625,22 @@
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193558</v>
+        <v>560.6592858193557</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657396</v>
+        <v>4406.934138657397</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888539</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252181</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4652.873020834729</v>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1659464.078106953</v>
+        <v>799313.652444598</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>4367.58902901592</v>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1398080.396311236</v>
+        <v>654592.2248359029</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>231.1379249870064</v>
@@ -17763,22 +17763,22 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.11633837899</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>410.0571917407942</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810829</v>
+        <v>4860.049068810828</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375967</v>
+        <v>7725.953271892038</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303852</v>
+        <v>2462.699113100389</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224321</v>
@@ -17790,22 +17790,22 @@
         <v>5497.210231316723</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.61799146968</v>
+        <v>8533.720644266217</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.764857629416</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>448.2773868014747</v>
+        <v>448.2773868014774</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>165.507746920809</v>
+        <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292747</v>
+        <v>9544.356383217537</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>1246929.378315747</v>
+        <v>608585.6443209094</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>181.9507484172754</v>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>1024270.553274606</v>
+        <v>501271.2572334952</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>4715.065128560275</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>884256.2432951635</v>
+        <v>428897.0066517743</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2371.245811243431</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>805463.0946363324</v>
+        <v>391991.7338640624</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2463.75639809482</v>
@@ -18108,34 +18108,34 @@
         <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996084</v>
+        <v>32493.07951996085</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233702</v>
+        <v>1367.292909233701</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>3448.841300635404</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288215</v>
+        <v>41401.49046288216</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700119</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>1383.30169709932</v>
+        <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>765179.3256439532</v>
+        <v>378585.3350421691</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>524.462996491248</v>
@@ -18165,16 +18165,16 @@
         <v>7613</v>
       </c>
       <c r="F68" s="143" t="n">
-        <v>2937</v>
+        <v>2947</v>
       </c>
       <c r="G68" s="143" t="n">
         <v>8960</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>45224</v>
+        <v>45234</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.68525504045</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>6296.901716791413</v>
@@ -18186,37 +18186,37 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342014</v>
+        <v>62122.79635693621</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.39453944851</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411189</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870798</v>
+        <v>2439.116021870797</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>14003.7821663689</v>
+        <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630283</v>
+        <v>64372.37424909938</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.82584599084</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275839</v>
+        <v>6878.522835275841</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2535.996836477479</v>
+        <v>2535.996836477478</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.45769810819</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>482250.6227778763</v>
+        <v>231954.5763626385</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>1895.838675356806</v>
@@ -18725,7 +18725,7 @@
         <v>42.9367881661009</v>
       </c>
       <c r="L76" s="131" t="n">
-        <v>12.11019747209272</v>
+        <v>12.11019747209273</v>
       </c>
       <c r="M76" s="131" t="n">
         <v>0</v>
@@ -18734,10 +18734,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399727</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -18746,13 +18746,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05577202167449</v>
+        <v>45.0557720216745</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -18792,7 +18792,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -18807,10 +18807,10 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328252</v>
+        <v>51.04086451328254</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
         <v>428.5976195989508</v>
@@ -18822,13 +18822,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239313</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>486.2580302793616</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217548</v>
+        <v>542.1736389217547</v>
       </c>
     </row>
     <row r="78">
@@ -18920,13 +18920,13 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486969</v>
+        <v>2697.069435486968</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.2101537440751</v>
+        <v>51.21015374407511</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
@@ -18935,34 +18935,34 @@
         <v>2871.031146169767</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277549</v>
+        <v>2967.818385277547</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936018</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.05193641638</v>
+        <v>3183.051936416378</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>3245.047703850661</v>
+        <v>3245.047703850659</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598369</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3500.166070420847</v>
+        <v>3500.166070420846</v>
       </c>
     </row>
     <row r="80">
@@ -19347,7 +19347,7 @@
         <v>252563.5334183737</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897596</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>1395.789484341961</v>
@@ -19362,7 +19362,7 @@
         <v>253578.7535428639</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879695</v>
+        <v>58272.40781879696</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
@@ -19414,7 +19414,7 @@
         <v>252748.9987789858</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323378</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
         <v>3262.529604664169</v>
@@ -19429,7 +19429,7 @@
         <v>253794.7078852251</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624421</v>
+        <v>58414.03815624422</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>3611.957540811319</v>
@@ -19924,13 +19924,13 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748546</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471617</v>
+        <v>287.3141106471616</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -19939,13 +19939,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901525</v>
+        <v>3803.886503901526</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483363</v>
+        <v>289.1404209483361</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -19954,13 +19954,13 @@
         <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -20012,13 +20012,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665506</v>
+        <v>456.6186053665505</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049632</v>
+        <v>5331.246709049631</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -20027,13 +20027,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>516.3191201840586</v>
+        <v>516.3191201840584</v>
       </c>
       <c r="Y95" s="131" t="n">
         <v>5418.203064292061</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5934.52218447612</v>
+        <v>5934.522184476119</v>
       </c>
     </row>
     <row r="96">
@@ -20116,16 +20116,16 @@
         <v>6698</v>
       </c>
       <c r="F97" s="131" t="n">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="G97" s="131" t="n">
         <v>3193</v>
       </c>
       <c r="H97" s="132" t="n">
-        <v>35946</v>
+        <v>35956</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5407.544268747402</v>
+        <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>821.8541182771896</v>
@@ -20134,37 +20134,37 @@
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410619</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>7069.112073998889</v>
+        <v>7069.112073998888</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427484</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.3963514921278</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.6295457533571</v>
+        <v>300.629545753357</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008077</v>
+        <v>571.6795744008076</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073776</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299142</v>
       </c>
       <c r="Z97" s="132" t="n">
         <v>8153.039091255576</v>
@@ -20259,7 +20259,7 @@
         <v>3922</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2315.017224862706</v>
+        <v>2315.11633837875</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>410.0571917407797</v>
@@ -20268,13 +20268,13 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571753</v>
+        <v>6263.925439571751</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136659</v>
+        <v>9129.829642652701</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2462.596460303757</v>
+        <v>2462.699113100301</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>422.0057850224257</v>
@@ -20283,13 +20283,13 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971808</v>
+        <v>6975.373307971809</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.88372092121</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2639.658250704873</v>
+        <v>2639.764857629547</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>448.277386801492</v>
@@ -20298,10 +20298,10 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578744</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11118.07690593058</v>
       </c>
     </row>
     <row r="100">
@@ -20552,10 +20552,10 @@
         <v>256655.8101514259</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820966</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977366</v>
+        <v>4844.630784977365</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469095.27040621</v>
@@ -20567,7 +20567,7 @@
         <v>257981.429150564</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589627</v>
+        <v>59655.70951589628</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -20589,16 +20589,16 @@
         <v>7839</v>
       </c>
       <c r="F104" s="143" t="n">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G104" s="143" t="n">
         <v>10545</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>48702</v>
+        <v>48712</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204109</v>
+        <v>1147367.743317625</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>257480.6278357822</v>
@@ -20610,10 +20610,10 @@
         <v>15819.80035996352</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1480444.654269834</v>
+        <v>1480444.75338335</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.46897923</v>
+        <v>1160502.571632026</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>259202.0803003969</v>
@@ -20625,22 +20625,22 @@
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195764</v>
+        <v>1497344.281848561</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554632</v>
+        <v>1172449.123161557</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>260673.2307205009</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272169</v>
+        <v>60950.0349927217</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.35198903</v>
+        <v>1513285.458595955</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -20651,7 +20651,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -21632,13 +21632,13 @@
         <v>2948530.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2824301</v>
+        <v>2824325</v>
       </c>
       <c r="G25" s="41" t="n">
         <v>25.52310030986256</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.44774246044112</v>
+        <v>24.44795020948028</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55708663.09676258</v>
+        <v>26604184.73231333</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379247</v>
+        <v>68660.92484379244</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21750,7 +21750,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>26145786.83676073</v>
+        <v>12307133.17526375</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1727.330050412035</v>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>16419605.75669</v>
+        <v>7728903.933722544</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>964.0204682757308</v>
@@ -21863,13 +21863,13 @@
         <v>5319254.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5520183</v>
+        <v>5520207</v>
       </c>
       <c r="G28" s="67" t="n">
         <v>36.1504838183597</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.51602533606992</v>
+        <v>37.51618844381618</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>14533745.03262174</v>
+        <v>7023342.719431079</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>17641.43818058407</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>13791214.6771605</v>
+        <v>6523260.719107439</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>6257.992427689866</v>
@@ -22017,13 +22017,13 @@
         <v>5538692.390034735</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5928219</v>
+        <v>5928243</v>
       </c>
       <c r="G30" s="72" t="n">
         <v>35.5354179928318</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.03456218241544</v>
+        <v>38.0347161628086</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>12177767.57492063</v>
+        <v>5732220.19508077</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>1286.37431571178</v>
@@ -22121,10 +22121,10 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>11466700.78725937</v>
+        <v>5397512.591638137</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>519.632056138488</v>
+        <v>519.6320561384879</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>11120783.4021973</v>
+        <v>5300011.277487393</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>13115.78537471264</v>
@@ -22269,10 +22269,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6911884.267178865</v>
+        <v>3276486.053190066</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>833.5527624453042</v>
+        <v>833.5527624453041</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>6215534.477519744</v>
+        <v>2962237.608184818</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>11475.85439019639</v>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>4120508.482950411</v>
+        <v>1963777.2483101</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3734.68760967116</v>
@@ -22500,10 +22500,10 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3859192.87246397</v>
+        <v>1816568.035491835</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>377.9510992814207</v>
+        <v>377.9510992814206</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>3464209.168802699</v>
+        <v>1680819.273526597</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>11271.648789632</v>
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>3041768.766676023</v>
+        <v>1449664.846786467</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>5996.680645260308</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2917567.158940644</v>
+        <v>1390472.081504347</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>2574.249362596877</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>2776564.194416662</v>
+        <v>1324575.504385623</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>0</v>
@@ -22820,13 +22820,13 @@
         <v>50296108.41710961</v>
       </c>
       <c r="F41" s="40" t="n">
-        <v>28661163</v>
+        <v>28661187</v>
       </c>
       <c r="G41" s="41" t="n">
         <v>42.46418414934163</v>
       </c>
       <c r="H41" s="42" t="n">
-        <v>24.19815253842335</v>
+        <v>24.19817280123198</v>
       </c>
       <c r="I41" s="31" t="n"/>
       <c r="J41" s="31" t="n"/>
@@ -22861,7 +22861,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2458690.660593475</v>
+        <v>1157334.968942554</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>404.9080956923283</v>
@@ -22938,7 +22938,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>2415536.179669428</v>
+        <v>1115944.625470568</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>0</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>2148315.559466744</v>
+        <v>1023857.428112992</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2279.367955575647</v>
@@ -23051,13 +23051,13 @@
         <v>84625120.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57905081</v>
+        <v>57905105</v>
       </c>
       <c r="G44" s="67" t="n">
         <v>55.73554683789877</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13727357569123</v>
+        <v>38.13728938250041</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1963068.780251959</v>
+        <v>942340.3361992717</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2764.956425043126</v>
@@ -23170,13 +23170,13 @@
         <v>84894979.79706067</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58345311</v>
+        <v>58345335</v>
       </c>
       <c r="G46" s="72" t="n">
         <v>55.56026898065463</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18460385607141</v>
+        <v>38.18461956308329</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>82313557.8754483</v>
+        <v>38768951.60905594</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>8338.628013770052</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>69766127.77131443</v>
+        <v>33307436.27990537</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>85020.26381129168</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>16071644.46334269</v>
+        <v>7765876.720099068</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>19394.604265202</v>
@@ -23449,10 +23449,10 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>15855936.75445963</v>
+        <v>7489885.191179895</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>6928.785556376583</v>
+        <v>6928.785556376582</v>
       </c>
     </row>
     <row r="53">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>12617317.80718354</v>
+        <v>6020019.459657344</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>13490.22172766402</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>9810448.624385368</v>
+        <v>4675523.87866664</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>23659.13977320257</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3819537.732706298</v>
+        <v>1875267.391436376</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>10530.01980578507</v>
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3777216.039146743</v>
+        <v>1833223.844701902</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>12535.421478272</v>
@@ -23850,14 +23850,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>GROWTH HORMONES</t>
+          <t>NARCOLEPSY</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>3235667.48750357</v>
+        <v>1514652.658129947</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>415.652658086724</v>
+        <v>251.5675531601408</v>
       </c>
     </row>
     <row r="58">
@@ -23882,37 +23882,37 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410514</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.73362042244</v>
+        <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831596</v>
+        <v>276.6926051831595</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842926</v>
+        <v>5127.579913842927</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -23924,21 +23924,21 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>NARCOLEPSY</t>
+          <t>GROWTH HORMONES</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>3173681.036372458</v>
+        <v>1511577.157088639</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>251.5675531601408</v>
+        <v>415.652658086724</v>
       </c>
     </row>
     <row r="59">
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -23984,13 +23984,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.577740853268</v>
+        <v>405.5777408532679</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597413</v>
+        <v>4497.071348597412</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.649089450681</v>
+        <v>4902.64908945068</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>460.4035115416655</v>
+        <v>460.4035115416654</v>
       </c>
       <c r="Y59" s="131" t="n">
         <v>4931.9450340127</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>2628647.02892981</v>
+        <v>1214398.918502162</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>2504114.100329963</v>
+        <v>1156866.411419562</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>0</v>
@@ -24116,16 +24116,16 @@
         <v>6511</v>
       </c>
       <c r="F61" s="131" t="n">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="G61" s="131" t="n">
         <v>2450</v>
       </c>
       <c r="H61" s="132" t="n">
-        <v>33507</v>
+        <v>33517</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2710.474833260433</v>
+        <v>2710.474833260434</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>710.0358767901117</v>
@@ -24134,13 +24134,13 @@
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894161</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2848.462218149934</v>
+        <v>2848.462218149935</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>760.0653829141091</v>
@@ -24149,22 +24149,22 @@
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193558</v>
+        <v>560.6592858193557</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657396</v>
+        <v>4406.934138657397</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888539</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252181</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4652.873020834729</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1645939.729946921</v>
+        <v>785510.5823583755</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>4163.666297251169</v>
@@ -24259,10 +24259,10 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1429319.996238187</v>
+        <v>660326.2585360666</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>217.5932425827678</v>
+        <v>217.5932425827679</v>
       </c>
     </row>
     <row r="63">
@@ -24287,22 +24287,22 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.11633837899</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>410.0571917407942</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810829</v>
+        <v>4860.049068810828</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375967</v>
+        <v>7725.953271892038</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303852</v>
+        <v>2462.699113100389</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224321</v>
@@ -24314,22 +24314,22 @@
         <v>5497.210231316723</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.61799146968</v>
+        <v>8533.720644266217</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.764857629416</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>448.2773868014747</v>
+        <v>448.2773868014774</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>165.507746920809</v>
+        <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292747</v>
+        <v>9544.356383217537</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>1255610.070590963</v>
+        <v>605401.0752094832</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>186.4773767285392</v>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>1053777.33709058</v>
+        <v>512871.7094225382</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>4831.904442445998</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>809501.5421693429</v>
+        <v>399394.2368961711</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>539.0692909435292</v>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>776964.8098135071</v>
+        <v>375098.6910898471</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2348.723611867773</v>
@@ -24632,48 +24632,48 @@
         <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996084</v>
+        <v>32493.07951996085</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233702</v>
+        <v>1367.292909233701</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>3448.841300635404</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288215</v>
+        <v>41401.49046288216</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700119</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>1383.30169709932</v>
+        <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>ADHD &amp; NARCOLEPSY MEDICATIONS</t>
+          <t>ANTIPSORIATICS - TOPICAL</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>531715.2618818849</v>
+        <v>256256.0202100373</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>1989.888009309796</v>
+        <v>539.1851296589119</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24689,16 +24689,16 @@
         <v>7613</v>
       </c>
       <c r="F68" s="143" t="n">
-        <v>2937</v>
+        <v>2947</v>
       </c>
       <c r="G68" s="143" t="n">
         <v>8960</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>45224</v>
+        <v>45234</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.68525504045</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>6296.901716791413</v>
@@ -24710,51 +24710,51 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342014</v>
+        <v>62122.79635693621</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.39453944851</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411189</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870798</v>
+        <v>2439.116021870797</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>14003.7821663689</v>
+        <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630283</v>
+        <v>64372.37424909938</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.82584599084</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275839</v>
+        <v>6878.522835275841</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2535.996836477479</v>
+        <v>2535.996836477478</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.45769810819</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>ANTIPSORIATICS - TOPICAL</t>
+          <t>ADHD &amp; NARCOLEPSY MEDICATIONS</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>513189.3884724432</v>
+        <v>253408.1262502909</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>539.1851296589119</v>
+        <v>1989.888009309796</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -25249,7 +25249,7 @@
         <v>42.9367881661009</v>
       </c>
       <c r="L76" s="131" t="n">
-        <v>12.11019747209272</v>
+        <v>12.11019747209273</v>
       </c>
       <c r="M76" s="131" t="n">
         <v>0</v>
@@ -25258,10 +25258,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399727</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -25270,13 +25270,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05577202167449</v>
+        <v>45.0557720216745</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -25316,7 +25316,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -25331,10 +25331,10 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328252</v>
+        <v>51.04086451328254</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
         <v>428.5976195989508</v>
@@ -25346,13 +25346,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239313</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>486.2580302793616</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217548</v>
+        <v>542.1736389217547</v>
       </c>
     </row>
     <row r="78">
@@ -25444,13 +25444,13 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486969</v>
+        <v>2697.069435486968</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.2101537440751</v>
+        <v>51.21015374407511</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
@@ -25459,34 +25459,34 @@
         <v>2871.031146169767</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277549</v>
+        <v>2967.818385277547</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936018</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.05193641638</v>
+        <v>3183.051936416378</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>3245.047703850661</v>
+        <v>3245.047703850659</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598369</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3500.166070420847</v>
+        <v>3500.166070420846</v>
       </c>
     </row>
     <row r="80">
@@ -25871,7 +25871,7 @@
         <v>252563.5334183737</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897596</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>1395.789484341961</v>
@@ -25886,7 +25886,7 @@
         <v>253578.7535428639</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879695</v>
+        <v>58272.40781879696</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
@@ -25938,7 +25938,7 @@
         <v>252748.9987789858</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323378</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
         <v>3262.529604664169</v>
@@ -25953,7 +25953,7 @@
         <v>253794.7078852251</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624421</v>
+        <v>58414.03815624422</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>3611.957540811319</v>
@@ -26448,13 +26448,13 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748546</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471617</v>
+        <v>287.3141106471616</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -26463,13 +26463,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901525</v>
+        <v>3803.886503901526</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483363</v>
+        <v>289.1404209483361</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -26478,13 +26478,13 @@
         <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -26536,13 +26536,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665506</v>
+        <v>456.6186053665505</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049632</v>
+        <v>5331.246709049631</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -26551,13 +26551,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>516.3191201840586</v>
+        <v>516.3191201840584</v>
       </c>
       <c r="Y95" s="131" t="n">
         <v>5418.203064292061</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5934.52218447612</v>
+        <v>5934.522184476119</v>
       </c>
     </row>
     <row r="96">
@@ -26640,16 +26640,16 @@
         <v>6698</v>
       </c>
       <c r="F97" s="131" t="n">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="G97" s="131" t="n">
         <v>3193</v>
       </c>
       <c r="H97" s="132" t="n">
-        <v>35946</v>
+        <v>35956</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5407.544268747402</v>
+        <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>821.8541182771896</v>
@@ -26658,37 +26658,37 @@
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410619</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>7069.112073998889</v>
+        <v>7069.112073998888</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427484</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.3963514921278</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.6295457533571</v>
+        <v>300.629545753357</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008077</v>
+        <v>571.6795744008076</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073776</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299142</v>
       </c>
       <c r="Z97" s="132" t="n">
         <v>8153.039091255576</v>
@@ -26783,7 +26783,7 @@
         <v>3922</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2315.017224862706</v>
+        <v>2315.11633837875</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>410.0571917407797</v>
@@ -26792,13 +26792,13 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571753</v>
+        <v>6263.925439571751</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136659</v>
+        <v>9129.829642652701</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2462.596460303757</v>
+        <v>2462.699113100301</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>422.0057850224257</v>
@@ -26807,13 +26807,13 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971808</v>
+        <v>6975.373307971809</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.88372092121</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2639.658250704873</v>
+        <v>2639.764857629547</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>448.277386801492</v>
@@ -26822,10 +26822,10 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578744</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11118.07690593058</v>
       </c>
     </row>
     <row r="100">
@@ -27076,10 +27076,10 @@
         <v>256655.8101514259</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820966</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977366</v>
+        <v>4844.630784977365</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469095.27040621</v>
@@ -27091,7 +27091,7 @@
         <v>257981.429150564</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589627</v>
+        <v>59655.70951589628</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -27113,16 +27113,16 @@
         <v>7839</v>
       </c>
       <c r="F104" s="143" t="n">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G104" s="143" t="n">
         <v>10545</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>48702</v>
+        <v>48712</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204109</v>
+        <v>1147367.743317625</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>257480.6278357822</v>
@@ -27134,10 +27134,10 @@
         <v>15819.80035996352</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1480444.654269834</v>
+        <v>1480444.75338335</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.46897923</v>
+        <v>1160502.571632026</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>259202.0803003969</v>
@@ -27149,22 +27149,22 @@
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195764</v>
+        <v>1497344.281848561</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554632</v>
+        <v>1172449.123161557</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>260673.2307205009</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272169</v>
+        <v>60950.0349927217</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.35198903</v>
+        <v>1513285.458595955</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -27175,7 +27175,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -28156,13 +28156,13 @@
         <v>2948530.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2824301</v>
+        <v>2824325</v>
       </c>
       <c r="G25" s="41" t="n">
         <v>25.52310030986256</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.44774246044112</v>
+        <v>24.44795020948028</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -28197,10 +28197,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>69272530.81205237</v>
+        <v>32788239.0805704</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.10616487113</v>
+        <v>82393.10616487109</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28274,10 +28274,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>33438837.92872162</v>
+        <v>15524842.09406595</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>2045.210599589361</v>
+        <v>2045.210599589362</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -28351,7 +28351,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>21510242.08687595</v>
+        <v>9986684.122089271</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>1141.429155052513</v>
@@ -28387,13 +28387,13 @@
         <v>5319254.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5520183</v>
+        <v>5520207</v>
       </c>
       <c r="G28" s="67" t="n">
         <v>36.1504838183597</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.51602533606992</v>
+        <v>37.51618844381618</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -28428,10 +28428,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>17997075.01372882</v>
+        <v>8393220.520934569</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>7591.883513651962</v>
+        <v>7591.883513651961</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>16602094.39170929</v>
+        <v>7969347.867944976</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>19791.41132971137</v>
@@ -28541,13 +28541,13 @@
         <v>5538692.390034735</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5928219</v>
+        <v>5928243</v>
       </c>
       <c r="G30" s="72" t="n">
         <v>35.5354179928318</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.03456218241544</v>
+        <v>38.0347161628086</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>15778357.57624285</v>
+        <v>7325509.05019576</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>1523.105781032218</v>
@@ -28645,10 +28645,10 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>12205251.53890275</v>
+        <v>5666602.507650739</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>529.9779303762052</v>
+        <v>529.9779303762053</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>11231931.67480008</v>
+        <v>5305992.084605201</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>12591.15395972414</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>7683964.371641369</v>
+        <v>3590795.25266048</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>850.356497390649</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>6672923.775079137</v>
+        <v>3152305.565674121</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>11760.22606198546</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>4926619.053816584</v>
+        <v>2376139.045184284</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>15780.3083054848</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>4650619.172496125</v>
+        <v>2196963.908990021</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>3987.994031430143</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>4287898.964534461</v>
+        <v>1990767.576361508</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>385.5828701423581</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>3344521.812389606</v>
+        <v>1579960.311114032</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2764.898270390802</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>3252150.948696879</v>
+        <v>1537767.603483175</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>0</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>3197540.665934136</v>
+        <v>1510526.056859382</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>6145.278391649857</v>
@@ -29344,13 +29344,13 @@
         <v>50296108.41710961</v>
       </c>
       <c r="F41" s="40" t="n">
-        <v>28661163</v>
+        <v>28661187</v>
       </c>
       <c r="G41" s="41" t="n">
         <v>42.46418414934163</v>
       </c>
       <c r="H41" s="42" t="n">
-        <v>24.19815253842335</v>
+        <v>24.19817280123198</v>
       </c>
       <c r="I41" s="31" t="n"/>
       <c r="J41" s="31" t="n"/>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>3026056.150974268</v>
+        <v>1380737.436178788</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>0</v>
@@ -29404,7 +29404,7 @@
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>418.9450962243398</v>
+        <v>418.9450962243399</v>
       </c>
     </row>
     <row r="42">
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>2684112.682049274</v>
+        <v>1246168.471533601</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>412.9698158775626</v>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>2476876.419150952</v>
+        <v>1170082.498279989</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2448.177946365579</v>
@@ -29575,13 +29575,13 @@
         <v>84625120.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57905081</v>
+        <v>57905105</v>
       </c>
       <c r="G44" s="67" t="n">
         <v>55.73554683789877</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13727357569123</v>
+        <v>38.13728938250041</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>2260678.222648065</v>
+        <v>1075309.607748776</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2957.226786839574</v>
@@ -29694,13 +29694,13 @@
         <v>84894979.79706067</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58345311</v>
+        <v>58345335</v>
       </c>
       <c r="G46" s="72" t="n">
         <v>55.56026898065463</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18460385607141</v>
+        <v>38.18461956308329</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>100761024.1361903</v>
+        <v>46804218.47342984</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>9156.756912025601</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>83433887.32809941</v>
+        <v>39481539.48019859</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>98089.90734281891</v>
@@ -29852,10 +29852,10 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>20273969.19879542</v>
+        <v>9445955.795633601</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>8258.907574637857</v>
+        <v>8258.907574637855</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>18417590.23703323</v>
+        <v>8839953.407201558</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>21753.62464832416</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>14382366.90474352</v>
+        <v>6801637.771185922</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>14453.52069515931</v>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>10453770.59422026</v>
+        <v>4938386.880651906</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>24245.41325678253</v>
@@ -30216,7 +30216,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>5384222.665782684</v>
+        <v>2597727.726072642</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>17549.5900695808</v>
@@ -30297,7 +30297,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3700107.459764481</v>
+        <v>1750337.532134253</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>251.6271412030642</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>3527213.610279341</v>
+        <v>1626144.176002181</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>423.5708412232761</v>
@@ -30406,37 +30406,37 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410514</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5043.97753572962</v>
+        <v>5043.977535729621</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>3672.153688237326</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1178.73362042244</v>
+        <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831596</v>
+        <v>276.6926051831595</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842926</v>
+        <v>5127.579913842927</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -30448,21 +30448,21 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>PCSK9 INHIBITORS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>3140461.981709545</v>
+        <v>1468198.194281557</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>0</v>
+        <v>8851.53234581861</v>
       </c>
     </row>
     <row r="59">
@@ -30493,7 +30493,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
         <v>4111.798092690687</v>
@@ -30508,13 +30508,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.577740853268</v>
+        <v>405.5777408532679</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597413</v>
+        <v>4497.071348597412</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.649089450681</v>
+        <v>4902.64908945068</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -30523,7 +30523,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>460.4035115416655</v>
+        <v>460.4035115416654</v>
       </c>
       <c r="Y59" s="131" t="n">
         <v>4931.9450340127</v>
@@ -30536,11 +30536,11 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>ASTHMA</t>
+          <t>PCSK9 INHIBITORS</t>
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>3132327.10108017</v>
+        <v>1432938.8513318</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -30617,14 +30617,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>ASTHMA</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>3004949.769884242</v>
+        <v>1429227.045052128</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>8851.532345818609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -30640,16 +30640,16 @@
         <v>6511</v>
       </c>
       <c r="F61" s="131" t="n">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="G61" s="131" t="n">
         <v>2450</v>
       </c>
       <c r="H61" s="132" t="n">
-        <v>33507</v>
+        <v>33517</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2710.474833260433</v>
+        <v>2710.474833260434</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>710.0358767901117</v>
@@ -30658,13 +30658,13 @@
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894161</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2848.462218149934</v>
+        <v>2848.462218149935</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>760.0653829141091</v>
@@ -30673,22 +30673,22 @@
         <v>237.7472517739969</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193558</v>
+        <v>560.6592858193557</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4406.934138657396</v>
+        <v>4406.934138657397</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.249027688854</v>
+        <v>816.2490276888539</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252181</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4652.873020834729</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1648202.438743794</v>
+        <v>779646.9554433154</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>3969.264717832511</v>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1473435.555221174</v>
+        <v>672303.3312636147</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>204.8422785674177</v>
@@ -30811,22 +30811,22 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862917</v>
+        <v>2315.11633837899</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>410.0571917407942</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810829</v>
+        <v>4860.049068810828</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375967</v>
+        <v>7725.953271892038</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303852</v>
+        <v>2462.699113100389</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224321</v>
@@ -30838,22 +30838,22 @@
         <v>5497.210231316723</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.61799146968</v>
+        <v>8533.720644266217</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.764857629416</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>448.2773868014747</v>
+        <v>448.2773868014774</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>165.507746920809</v>
+        <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865837</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292747</v>
+        <v>9544.356383217537</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30864,7 +30864,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>1175911.787801981</v>
+        <v>560647.5700983753</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>168.5668759667755</v>
@@ -30945,7 +30945,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>1094948.346245071</v>
+        <v>530034.7198486113</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>4951.639034529811</v>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>865134.1989801429</v>
+        <v>425656.8292348867</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>554.0823706963065</v>
@@ -31113,7 +31113,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>756754.0129428871</v>
+        <v>362516.031487516</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2239.061706429667</v>
@@ -31156,34 +31156,34 @@
         <v>40682.42166411847</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>32493.07951996084</v>
+        <v>32493.07951996085</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233702</v>
+        <v>1367.292909233701</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>3448.841300635404</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288215</v>
+        <v>41401.49046288216</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700119</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>1383.30169709932</v>
+        <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>3796.051969460277</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>627466.5953169058</v>
+        <v>313229.7004550081</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>636.2384529975162</v>
@@ -31213,16 +31213,16 @@
         <v>7613</v>
       </c>
       <c r="F68" s="143" t="n">
-        <v>2937</v>
+        <v>2947</v>
       </c>
       <c r="G68" s="143" t="n">
         <v>8960</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>45224</v>
+        <v>45234</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.68525504045</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>6296.901716791413</v>
@@ -31234,37 +31234,37 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342014</v>
+        <v>62122.79635693621</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.39453944851</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411189</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870798</v>
+        <v>2439.116021870797</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>14003.7821663689</v>
+        <v>14003.78216636889</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>64372.27159630283</v>
+        <v>64372.37424909938</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.82584599084</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>6878.522835275839</v>
+        <v>6878.522835275841</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2535.996836477479</v>
+        <v>2535.996836477478</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.45769810819</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31275,7 +31275,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>607398.58831547</v>
+        <v>277145.5411689248</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>68.67129630503629</v>
@@ -31773,7 +31773,7 @@
         <v>42.9367881661009</v>
       </c>
       <c r="L76" s="131" t="n">
-        <v>12.11019747209272</v>
+        <v>12.11019747209273</v>
       </c>
       <c r="M76" s="131" t="n">
         <v>0</v>
@@ -31782,10 +31782,10 @@
         <v>183.3291939762258</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399727</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -31794,13 +31794,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05577202167449</v>
+        <v>45.0557720216745</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -31840,7 +31840,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="131" t="n">
-        <v>46.76991949101995</v>
+        <v>46.76991949101996</v>
       </c>
       <c r="M77" s="131" t="n">
         <v>311.9992424177221</v>
@@ -31855,10 +31855,10 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.04086451328252</v>
+        <v>51.04086451328254</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>377.5567550856683</v>
+        <v>377.5567550856682</v>
       </c>
       <c r="T77" s="132" t="n">
         <v>428.5976195989508</v>
@@ -31870,13 +31870,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91560864239313</v>
+        <v>55.91560864239312</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>486.2580302793616</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>542.1736389217548</v>
+        <v>542.1736389217547</v>
       </c>
     </row>
     <row r="78">
@@ -31968,13 +31968,13 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486969</v>
+        <v>2697.069435486968</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.2101537440751</v>
+        <v>51.21015374407511</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
@@ -31983,34 +31983,34 @@
         <v>2871.031146169767</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277549</v>
+        <v>2967.818385277547</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88229397936017</v>
+        <v>62.88229397936018</v>
       </c>
       <c r="S79" s="131" t="n">
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.05193641638</v>
+        <v>3183.051936416378</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>3245.047703850661</v>
+        <v>3245.047703850659</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>170.8985703395071</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.00721802598373</v>
+        <v>73.00721802598369</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>11.21257820469615</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3500.166070420847</v>
+        <v>3500.166070420846</v>
       </c>
     </row>
     <row r="80">
@@ -32395,7 +32395,7 @@
         <v>252563.5334183737</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>57807.83114897596</v>
+        <v>57807.83114897595</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>1395.789484341961</v>
@@ -32410,7 +32410,7 @@
         <v>253578.7535428639</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>58272.40781879695</v>
+        <v>58272.40781879696</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>1540.766409614355</v>
@@ -32462,7 +32462,7 @@
         <v>252748.9987789858</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>57934.20212323378</v>
+        <v>57934.20212323377</v>
       </c>
       <c r="S86" s="143" t="n">
         <v>3262.529604664169</v>
@@ -32477,7 +32477,7 @@
         <v>253794.7078852251</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58414.03815624421</v>
+        <v>58414.03815624422</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>3611.957540811319</v>
@@ -32972,13 +32972,13 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748546</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>287.3141106471617</v>
+        <v>287.3141106471616</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -32987,13 +32987,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901525</v>
+        <v>3803.886503901526</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483363</v>
+        <v>289.1404209483361</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -33002,13 +33002,13 @@
         <v>5315.8949373063</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107066</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -33060,13 +33060,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665506</v>
+        <v>456.6186053665505</v>
       </c>
       <c r="S95" s="131" t="n">
         <v>4874.628103683081</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049632</v>
+        <v>5331.246709049631</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -33075,13 +33075,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>516.3191201840586</v>
+        <v>516.3191201840584</v>
       </c>
       <c r="Y95" s="131" t="n">
         <v>5418.203064292061</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5934.52218447612</v>
+        <v>5934.522184476119</v>
       </c>
     </row>
     <row r="96">
@@ -33164,16 +33164,16 @@
         <v>6698</v>
       </c>
       <c r="F97" s="131" t="n">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="G97" s="131" t="n">
         <v>3193</v>
       </c>
       <c r="H97" s="132" t="n">
-        <v>35946</v>
+        <v>35956</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5407.544268747402</v>
+        <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>821.8541182771896</v>
@@ -33182,37 +33182,37 @@
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410619</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>7069.112073998889</v>
+        <v>7069.112073998888</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5816.280603427484</v>
+        <v>5816.280603427483</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.3963514921278</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.6295457533571</v>
+        <v>300.629545753357</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008077</v>
+        <v>571.6795744008076</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7589.986075073776</v>
+        <v>7589.986075073775</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.655996720889</v>
+        <v>6250.655996720888</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>321.7141332764122</v>
+        <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299142</v>
       </c>
       <c r="Z97" s="132" t="n">
         <v>8153.039091255576</v>
@@ -33307,7 +33307,7 @@
         <v>3922</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>2315.017224862706</v>
+        <v>2315.11633837875</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>410.0571917407797</v>
@@ -33316,13 +33316,13 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571753</v>
+        <v>6263.925439571751</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136659</v>
+        <v>9129.829642652701</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2462.596460303757</v>
+        <v>2462.699113100301</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>422.0057850224257</v>
@@ -33331,13 +33331,13 @@
         <v>151.8055148266722</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>6975.373307971808</v>
+        <v>6975.373307971809</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>10011.78106812466</v>
+        <v>10011.88372092121</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2639.658250704873</v>
+        <v>2639.764857629547</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>448.277386801492</v>
@@ -33346,10 +33346,10 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578744</v>
+        <v>7864.526914578741</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>11117.97029900591</v>
+        <v>11118.07690593058</v>
       </c>
     </row>
     <row r="100">
@@ -33600,10 +33600,10 @@
         <v>256655.8101514259</v>
       </c>
       <c r="R103" s="140" t="n">
-        <v>59175.12405820966</v>
+        <v>59175.12405820965</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>4844.630784977366</v>
+        <v>4844.630784977365</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469095.27040621</v>
@@ -33615,7 +33615,7 @@
         <v>257981.429150564</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>59655.70951589627</v>
+        <v>59655.70951589628</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>5336.818379074632</v>
@@ -33637,16 +33637,16 @@
         <v>7839</v>
       </c>
       <c r="F104" s="143" t="n">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G104" s="143" t="n">
         <v>10545</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>48702</v>
+        <v>48712</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1147367.644204109</v>
+        <v>1147367.743317625</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>257480.6278357822</v>
@@ -33658,10 +33658,10 @@
         <v>15819.80035996352</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1480444.654269834</v>
+        <v>1480444.75338335</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1160502.46897923</v>
+        <v>1160502.571632026</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>259202.0803003969</v>
@@ -33673,22 +33673,22 @@
         <v>17266.31177103306</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1497344.179195764</v>
+        <v>1497344.281848561</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1172449.016554632</v>
+        <v>1172449.123161557</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>260673.2307205009</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>60950.03499272169</v>
+        <v>60950.0349927217</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>19213.06972117535</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1513285.35198903</v>
+        <v>1513285.458595955</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -33699,7 +33699,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
